--- a/Deliverables/phase2/sprint2/ASVS_5_0_Tracker_Updated.xlsx
+++ b/Deliverables/phase2/sprint2/ASVS_5_0_Tracker_Updated.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mei/IdeaProjects/desofs2026-thu_ffs_111/Deliverables/phase2/sprint2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beatrizoliveirasilva/ISEP/DESOFS_Project/Deliverables/phase2/sprint2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B571D27-2BF5-A340-9BCD-9D8E67E86882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283BE049-BE14-CE49-AE1C-EBDAE0235CCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="15980" tabRatio="500" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="15980" tabRatio="500" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="967">
   <si>
     <t>OWASP ASVS 5.0 – Compliance Tracker</t>
   </si>
@@ -2960,6 +2960,12 @@
   </si>
   <si>
     <t>lastDeviceId</t>
+  </si>
+  <si>
+    <t>Using Password Encoder with BCrypt algorithms</t>
+  </si>
+  <si>
+    <t>Using Secure Random</t>
   </si>
 </sst>
 </file>
@@ -3794,7 +3800,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="pt-PT"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -7613,7 +7619,9 @@
       <c r="F21" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G21" s="21"/>
+      <c r="G21" s="21" t="s">
+        <v>965</v>
+      </c>
       <c r="H21" s="21"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -7693,7 +7701,9 @@
       <c r="F25" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="16"/>
+      <c r="G25" s="16" t="s">
+        <v>966</v>
+      </c>
       <c r="H25" s="16"/>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
